--- a/resultados/ConR/criterioB/resumen_parametros_ConR.xlsx
+++ b/resultados/ConR/criterioB/resumen_parametros_ConR.xlsx
@@ -428,7 +428,7 @@
         <v>32</v>
       </c>
       <c r="F3">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H3">
         <v>5</v>
@@ -541,10 +541,10 @@
         <v>178347</v>
       </c>
       <c r="D9">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="F9">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="H9">
         <v>28</v>
@@ -560,7 +560,7 @@
         <v>448</v>
       </c>
       <c r="F10">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="H10">
         <v>76</v>
@@ -633,7 +633,7 @@
         <v>354288</v>
       </c>
       <c r="D14">
-        <v>568</v>
+        <v>572</v>
       </c>
       <c r="F14">
         <v>115</v>
@@ -790,7 +790,7 @@
         <v>160</v>
       </c>
       <c r="F22">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="H22">
         <v>29</v>

--- a/resultados/ConR/criterioB/resumen_parametros_ConR.xlsx
+++ b/resultados/ConR/criterioB/resumen_parametros_ConR.xlsx
@@ -403,13 +403,13 @@
         </is>
       </c>
       <c r="B2">
-        <v>216517</v>
+        <v>215569</v>
       </c>
       <c r="D2">
         <v>332</v>
       </c>
       <c r="F2">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="H2">
         <v>55</v>
@@ -422,13 +422,13 @@
         </is>
       </c>
       <c r="B3">
-        <v>2182.1</v>
+        <v>2172.7</v>
       </c>
       <c r="D3">
         <v>32</v>
       </c>
       <c r="F3">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H3">
         <v>5</v>
@@ -441,7 +441,7 @@
         </is>
       </c>
       <c r="B4">
-        <v>364520</v>
+        <v>362947</v>
       </c>
       <c r="D4">
         <v>52</v>
@@ -481,7 +481,7 @@
         </is>
       </c>
       <c r="B6">
-        <v>98432</v>
+        <v>19.8</v>
       </c>
       <c r="D6">
         <v>12</v>
@@ -500,7 +500,7 @@
         </is>
       </c>
       <c r="B7">
-        <v>11708.5</v>
+        <v>11656.4</v>
       </c>
       <c r="D7">
         <v>12</v>
@@ -519,7 +519,7 @@
         </is>
       </c>
       <c r="B8">
-        <v>164922</v>
+        <v>164196</v>
       </c>
       <c r="D8">
         <v>72</v>
@@ -538,10 +538,10 @@
         </is>
       </c>
       <c r="B9">
-        <v>178347</v>
+        <v>177567</v>
       </c>
       <c r="D9">
-        <v>188</v>
+        <v>184</v>
       </c>
       <c r="F9">
         <v>34</v>
@@ -556,14 +556,17 @@
           <t>Serpocaulon fraxinifolium</t>
         </is>
       </c>
+      <c r="B10">
+        <v>318579</v>
+      </c>
       <c r="D10">
-        <v>448</v>
+        <v>444</v>
       </c>
       <c r="F10">
         <v>91</v>
       </c>
       <c r="H10">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="11">
@@ -573,7 +576,7 @@
         </is>
       </c>
       <c r="B11">
-        <v>138336</v>
+        <v>137734</v>
       </c>
       <c r="D11">
         <v>116</v>
@@ -592,7 +595,7 @@
         </is>
       </c>
       <c r="B12">
-        <v>56700</v>
+        <v>56451</v>
       </c>
       <c r="D12">
         <v>48</v>
@@ -611,7 +614,7 @@
         </is>
       </c>
       <c r="B13">
-        <v>520184</v>
+        <v>517889</v>
       </c>
       <c r="D13">
         <v>124</v>
@@ -630,13 +633,13 @@
         </is>
       </c>
       <c r="B14">
-        <v>354288</v>
+        <v>352760</v>
       </c>
       <c r="D14">
         <v>572</v>
       </c>
       <c r="F14">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="H14">
         <v>89</v>
@@ -649,7 +652,7 @@
         </is>
       </c>
       <c r="B15">
-        <v>147427</v>
+        <v>146783</v>
       </c>
       <c r="D15">
         <v>28</v>
@@ -668,7 +671,7 @@
         </is>
       </c>
       <c r="B16">
-        <v>174510</v>
+        <v>173777</v>
       </c>
       <c r="D16">
         <v>52</v>
@@ -687,7 +690,7 @@
         </is>
       </c>
       <c r="B17">
-        <v>12305678</v>
+        <v>150114</v>
       </c>
       <c r="D17">
         <v>100</v>
@@ -696,7 +699,7 @@
         <v>20</v>
       </c>
       <c r="H17">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="18">
@@ -706,7 +709,7 @@
         </is>
       </c>
       <c r="B18">
-        <v>29789.9</v>
+        <v>29658.5</v>
       </c>
       <c r="D18">
         <v>32</v>
@@ -725,7 +728,7 @@
         </is>
       </c>
       <c r="B19">
-        <v>429306</v>
+        <v>427423</v>
       </c>
       <c r="D19">
         <v>80</v>
@@ -744,13 +747,13 @@
         </is>
       </c>
       <c r="B20">
-        <v>3075.6</v>
+        <v>3062.3</v>
       </c>
       <c r="D20">
         <v>28</v>
       </c>
       <c r="F20">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H20">
         <v>5</v>
@@ -784,16 +787,16 @@
         </is>
       </c>
       <c r="B22">
-        <v>11826902</v>
+        <v>195947</v>
       </c>
       <c r="D22">
-        <v>160</v>
+        <v>156</v>
       </c>
       <c r="F22">
         <v>33</v>
       </c>
       <c r="H22">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="23">
@@ -803,13 +806,13 @@
         </is>
       </c>
       <c r="B23">
-        <v>20887055</v>
+        <v>237219</v>
       </c>
       <c r="D23">
         <v>152</v>
       </c>
       <c r="F23">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="H23">
         <v>29</v>
@@ -822,7 +825,7 @@
         </is>
       </c>
       <c r="B24">
-        <v>992143</v>
+        <v>987791</v>
       </c>
       <c r="D24">
         <v>360</v>
@@ -841,7 +844,7 @@
         </is>
       </c>
       <c r="B25">
-        <v>74092</v>
+        <v>73775</v>
       </c>
       <c r="D25">
         <v>20</v>

--- a/resultados/ConR/criterioB/resumen_parametros_ConR.xlsx
+++ b/resultados/ConR/criterioB/resumen_parametros_ConR.xlsx
@@ -406,13 +406,13 @@
         <v>215569</v>
       </c>
       <c r="D2">
-        <v>332</v>
+        <v>336</v>
       </c>
       <c r="F2">
         <v>66</v>
       </c>
       <c r="H2">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="3">
@@ -425,7 +425,7 @@
         <v>2172.7</v>
       </c>
       <c r="D3">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="F3">
         <v>5</v>
@@ -541,7 +541,7 @@
         <v>177567</v>
       </c>
       <c r="D9">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="F9">
         <v>34</v>
@@ -639,7 +639,7 @@
         <v>572</v>
       </c>
       <c r="F14">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="H14">
         <v>89</v>
@@ -712,7 +712,7 @@
         <v>29658.5</v>
       </c>
       <c r="D18">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="F18">
         <v>5</v>
@@ -812,7 +812,7 @@
         <v>152</v>
       </c>
       <c r="F23">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="H23">
         <v>29</v>
@@ -831,7 +831,7 @@
         <v>360</v>
       </c>
       <c r="F24">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="H24">
         <v>76</v>

--- a/resultados/ConR/criterioB/resumen_parametros_ConR.xlsx
+++ b/resultados/ConR/criterioB/resumen_parametros_ConR.xlsx
@@ -409,7 +409,7 @@
         <v>336</v>
       </c>
       <c r="F2">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="H2">
         <v>56</v>
@@ -425,10 +425,10 @@
         <v>2172.7</v>
       </c>
       <c r="D3">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="F3">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H3">
         <v>5</v>
@@ -444,13 +444,13 @@
         <v>362947</v>
       </c>
       <c r="D4">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="F4">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H4">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="5">
@@ -459,19 +459,17 @@
           <t>Serpocaulon attenuatum</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>|EOO cannot be estimated because less than 3 unique pair of coordinates</t>
-        </is>
+      <c r="B5">
+        <v>10968.2</v>
       </c>
       <c r="D5">
+        <v>20</v>
+      </c>
+      <c r="F5">
         <v>4</v>
       </c>
-      <c r="F5">
-        <v>1</v>
-      </c>
       <c r="H5">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6">
@@ -500,16 +498,16 @@
         </is>
       </c>
       <c r="B7">
-        <v>11656.4</v>
+        <v>52105</v>
       </c>
       <c r="D7">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="F7">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H7">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="8">
@@ -560,10 +558,10 @@
         <v>318579</v>
       </c>
       <c r="D10">
-        <v>444</v>
+        <v>440</v>
       </c>
       <c r="F10">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="H10">
         <v>75</v>
@@ -636,10 +634,10 @@
         <v>352760</v>
       </c>
       <c r="D14">
-        <v>572</v>
+        <v>568</v>
       </c>
       <c r="F14">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="H14">
         <v>89</v>
@@ -652,16 +650,16 @@
         </is>
       </c>
       <c r="B15">
-        <v>146783</v>
+        <v>182539</v>
       </c>
       <c r="D15">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="F15">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H15">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="16">
@@ -712,7 +710,7 @@
         <v>29658.5</v>
       </c>
       <c r="D18">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="F18">
         <v>5</v>
@@ -765,19 +763,17 @@
           <t>Serpocaulon richardii</t>
         </is>
       </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>|EOO cannot be estimated because less than 3 unique pair of coordinates</t>
-        </is>
+      <c r="B21">
+        <v>4689.4</v>
       </c>
       <c r="D21">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="F21">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H21">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="22">
@@ -790,7 +786,7 @@
         <v>195947</v>
       </c>
       <c r="D22">
-        <v>156</v>
+        <v>160</v>
       </c>
       <c r="F22">
         <v>33</v>
@@ -828,10 +824,10 @@
         <v>987791</v>
       </c>
       <c r="D24">
-        <v>360</v>
+        <v>364</v>
       </c>
       <c r="F24">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="H24">
         <v>76</v>
@@ -844,16 +840,16 @@
         </is>
       </c>
       <c r="B25">
-        <v>73775</v>
+        <v>91473</v>
       </c>
       <c r="D25">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="F25">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H25">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>

--- a/resultados/ConR/criterioB/resumen_parametros_ConR.xlsx
+++ b/resultados/ConR/criterioB/resumen_parametros_ConR.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H25"/>
+  <dimension ref="A1:H27"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -403,13 +403,13 @@
         </is>
       </c>
       <c r="B2">
-        <v>215569</v>
+        <v>216517</v>
       </c>
       <c r="D2">
         <v>336</v>
       </c>
       <c r="F2">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="H2">
         <v>56</v>
@@ -422,13 +422,13 @@
         </is>
       </c>
       <c r="B3">
-        <v>2172.7</v>
+        <v>2182.1</v>
       </c>
       <c r="D3">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="F3">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H3">
         <v>5</v>
@@ -441,7 +441,7 @@
         </is>
       </c>
       <c r="B4">
-        <v>362947</v>
+        <v>364520</v>
       </c>
       <c r="D4">
         <v>56</v>
@@ -460,13 +460,13 @@
         </is>
       </c>
       <c r="B5">
-        <v>10968.2</v>
+        <v>11017.1</v>
       </c>
       <c r="D5">
         <v>20</v>
       </c>
       <c r="F5">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H5">
         <v>5</v>
@@ -479,7 +479,7 @@
         </is>
       </c>
       <c r="B6">
-        <v>19.8</v>
+        <v>19.9</v>
       </c>
       <c r="D6">
         <v>12</v>
@@ -498,7 +498,7 @@
         </is>
       </c>
       <c r="B7">
-        <v>52105</v>
+        <v>52337</v>
       </c>
       <c r="D7">
         <v>20</v>
@@ -517,7 +517,7 @@
         </is>
       </c>
       <c r="B8">
-        <v>164196</v>
+        <v>164922</v>
       </c>
       <c r="D8">
         <v>72</v>
@@ -536,10 +536,10 @@
         </is>
       </c>
       <c r="B9">
-        <v>177567</v>
+        <v>178347</v>
       </c>
       <c r="D9">
-        <v>188</v>
+        <v>184</v>
       </c>
       <c r="F9">
         <v>34</v>
@@ -555,13 +555,13 @@
         </is>
       </c>
       <c r="B10">
-        <v>318579</v>
+        <v>319959</v>
       </c>
       <c r="D10">
-        <v>440</v>
+        <v>444</v>
       </c>
       <c r="F10">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="H10">
         <v>75</v>
@@ -574,13 +574,13 @@
         </is>
       </c>
       <c r="B11">
-        <v>137734</v>
+        <v>138336</v>
       </c>
       <c r="D11">
         <v>116</v>
       </c>
       <c r="F11">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H11">
         <v>19</v>
@@ -593,7 +593,7 @@
         </is>
       </c>
       <c r="B12">
-        <v>56451</v>
+        <v>56700</v>
       </c>
       <c r="D12">
         <v>48</v>
@@ -612,7 +612,7 @@
         </is>
       </c>
       <c r="B13">
-        <v>517889</v>
+        <v>520184</v>
       </c>
       <c r="D13">
         <v>124</v>
@@ -631,7 +631,7 @@
         </is>
       </c>
       <c r="B14">
-        <v>352760</v>
+        <v>354288</v>
       </c>
       <c r="D14">
         <v>568</v>
@@ -650,7 +650,7 @@
         </is>
       </c>
       <c r="B15">
-        <v>182539</v>
+        <v>183341</v>
       </c>
       <c r="D15">
         <v>32</v>
@@ -669,7 +669,7 @@
         </is>
       </c>
       <c r="B16">
-        <v>173777</v>
+        <v>174510</v>
       </c>
       <c r="D16">
         <v>52</v>
@@ -688,7 +688,7 @@
         </is>
       </c>
       <c r="B17">
-        <v>150114</v>
+        <v>150772</v>
       </c>
       <c r="D17">
         <v>100</v>
@@ -707,7 +707,7 @@
         </is>
       </c>
       <c r="B18">
-        <v>29658.5</v>
+        <v>29789.9</v>
       </c>
       <c r="D18">
         <v>32</v>
@@ -722,133 +722,173 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Serpocaulon psychotrium</t>
+          <t>Serpocaulon polystichum</t>
         </is>
       </c>
       <c r="B19">
-        <v>427423</v>
+        <v>16703.4</v>
       </c>
       <c r="D19">
-        <v>80</v>
+        <v>12</v>
       </c>
       <c r="F19">
-        <v>17</v>
+        <v>3</v>
       </c>
       <c r="H19">
-        <v>17</v>
+        <v>3</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Serpocaulon ptilorhizon</t>
+          <t>Serpocaulon psychotrium</t>
         </is>
       </c>
       <c r="B20">
-        <v>3062.3</v>
+        <v>429306</v>
       </c>
       <c r="D20">
-        <v>28</v>
+        <v>80</v>
       </c>
       <c r="F20">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="H20">
-        <v>5</v>
+        <v>17</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Serpocaulon richardii</t>
+          <t>Serpocaulon ptilorhizon</t>
         </is>
       </c>
       <c r="B21">
-        <v>4689.4</v>
+        <v>3075.6</v>
       </c>
       <c r="D21">
-        <v>12</v>
+        <v>28</v>
       </c>
       <c r="F21">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="H21">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Serpocaulon sessilifolium</t>
+          <t>Serpocaulon richardii</t>
         </is>
       </c>
       <c r="B22">
-        <v>195947</v>
+        <v>7305.7</v>
       </c>
       <c r="D22">
-        <v>160</v>
+        <v>16</v>
       </c>
       <c r="F22">
-        <v>33</v>
+        <v>3</v>
       </c>
       <c r="H22">
-        <v>28</v>
+        <v>4</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Serpocaulon subandinum</t>
+          <t>Serpocaulon sessilifolium</t>
         </is>
       </c>
       <c r="B23">
-        <v>237219</v>
+        <v>196810</v>
       </c>
       <c r="D23">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="F23">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="H23">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Serpocaulon triseriale</t>
+          <t>Serpocaulon subandinum</t>
         </is>
       </c>
       <c r="B24">
-        <v>987791</v>
+        <v>238241</v>
       </c>
       <c r="D24">
-        <v>364</v>
+        <v>152</v>
       </c>
       <c r="F24">
-        <v>84</v>
+        <v>32</v>
       </c>
       <c r="H24">
-        <v>76</v>
+        <v>29</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
+          <t>Serpocaulon tayronae</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>|EOO cannot be estimated because less than 3 unique pair of coordinates</t>
+        </is>
+      </c>
+      <c r="D25">
+        <v>8</v>
+      </c>
+      <c r="F25">
+        <v>1</v>
+      </c>
+      <c r="H25">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Serpocaulon triseriale</t>
+        </is>
+      </c>
+      <c r="B26">
+        <v>992143</v>
+      </c>
+      <c r="D26">
+        <v>360</v>
+      </c>
+      <c r="F26">
+        <v>83</v>
+      </c>
+      <c r="H26">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
           <t>Serpocaulon wagneri</t>
         </is>
       </c>
-      <c r="B25">
-        <v>91473</v>
-      </c>
-      <c r="D25">
+      <c r="B27">
+        <v>91865</v>
+      </c>
+      <c r="D27">
         <v>28</v>
       </c>
-      <c r="F25">
+      <c r="F27">
         <v>6</v>
       </c>
-      <c r="H25">
+      <c r="H27">
         <v>6</v>
       </c>
     </row>

--- a/resultados/ConR/criterioB/resumen_parametros_ConR.xlsx
+++ b/resultados/ConR/criterioB/resumen_parametros_ConR.xlsx
@@ -425,10 +425,10 @@
         <v>2182.1</v>
       </c>
       <c r="D3">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="F3">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H3">
         <v>5</v>
@@ -466,7 +466,7 @@
         <v>20</v>
       </c>
       <c r="F5">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H5">
         <v>5</v>
@@ -542,7 +542,7 @@
         <v>184</v>
       </c>
       <c r="F9">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="H9">
         <v>28</v>
@@ -558,10 +558,10 @@
         <v>319959</v>
       </c>
       <c r="D10">
-        <v>444</v>
+        <v>440</v>
       </c>
       <c r="F10">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="H10">
         <v>75</v>
@@ -634,10 +634,10 @@
         <v>354288</v>
       </c>
       <c r="D14">
-        <v>568</v>
+        <v>572</v>
       </c>
       <c r="F14">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="H14">
         <v>89</v>
@@ -751,7 +751,7 @@
         <v>80</v>
       </c>
       <c r="F20">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="H20">
         <v>17</v>
@@ -770,7 +770,7 @@
         <v>28</v>
       </c>
       <c r="F21">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H21">
         <v>5</v>
@@ -789,7 +789,7 @@
         <v>16</v>
       </c>
       <c r="F22">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H22">
         <v>4</v>
@@ -805,7 +805,7 @@
         <v>196810</v>
       </c>
       <c r="D23">
-        <v>156</v>
+        <v>160</v>
       </c>
       <c r="F23">
         <v>33</v>
@@ -867,7 +867,7 @@
         <v>360</v>
       </c>
       <c r="F26">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="H26">
         <v>76</v>

--- a/resultados/ConR/criterioB/resumen_parametros_ConR.xlsx
+++ b/resultados/ConR/criterioB/resumen_parametros_ConR.xlsx
@@ -406,7 +406,7 @@
         <v>216517</v>
       </c>
       <c r="D2">
-        <v>336</v>
+        <v>332</v>
       </c>
       <c r="F2">
         <v>66</v>
@@ -428,7 +428,7 @@
         <v>32</v>
       </c>
       <c r="F3">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H3">
         <v>5</v>
@@ -539,10 +539,10 @@
         <v>178347</v>
       </c>
       <c r="D9">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="F9">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="H9">
         <v>28</v>
@@ -561,7 +561,7 @@
         <v>440</v>
       </c>
       <c r="F10">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="H10">
         <v>75</v>
@@ -580,7 +580,7 @@
         <v>116</v>
       </c>
       <c r="F11">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="H11">
         <v>19</v>
@@ -634,10 +634,10 @@
         <v>354288</v>
       </c>
       <c r="D14">
-        <v>572</v>
+        <v>568</v>
       </c>
       <c r="F14">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="H14">
         <v>89</v>
@@ -726,16 +726,16 @@
         </is>
       </c>
       <c r="B19">
-        <v>16703.4</v>
+        <v>171882</v>
       </c>
       <c r="D19">
-        <v>12</v>
+        <v>28</v>
       </c>
       <c r="F19">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="H19">
-        <v>3</v>
+        <v>7</v>
       </c>
     </row>
     <row r="20">
@@ -789,7 +789,7 @@
         <v>16</v>
       </c>
       <c r="F22">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H22">
         <v>4</v>
@@ -839,10 +839,8 @@
           <t>Serpocaulon tayronae</t>
         </is>
       </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>|EOO cannot be estimated because less than 3 unique pair of coordinates</t>
-        </is>
+      <c r="B25">
+        <v>0.373</v>
       </c>
       <c r="D25">
         <v>8</v>

--- a/resultados/ConR/criterioB/resumen_parametros_ConR.xlsx
+++ b/resultados/ConR/criterioB/resumen_parametros_ConR.xlsx
@@ -409,7 +409,7 @@
         <v>332</v>
       </c>
       <c r="F2">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="H2">
         <v>56</v>
@@ -425,7 +425,7 @@
         <v>2182.1</v>
       </c>
       <c r="D3">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="F3">
         <v>5</v>
@@ -558,10 +558,10 @@
         <v>319959</v>
       </c>
       <c r="D10">
-        <v>440</v>
+        <v>444</v>
       </c>
       <c r="F10">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="H10">
         <v>75</v>
@@ -637,7 +637,7 @@
         <v>568</v>
       </c>
       <c r="F14">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="H14">
         <v>89</v>
@@ -710,7 +710,7 @@
         <v>29789.9</v>
       </c>
       <c r="D18">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="F18">
         <v>5</v>
@@ -805,7 +805,7 @@
         <v>196810</v>
       </c>
       <c r="D23">
-        <v>160</v>
+        <v>156</v>
       </c>
       <c r="F23">
         <v>33</v>
@@ -827,7 +827,7 @@
         <v>152</v>
       </c>
       <c r="F24">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="H24">
         <v>29</v>
@@ -862,10 +862,10 @@
         <v>992143</v>
       </c>
       <c r="D26">
-        <v>360</v>
+        <v>364</v>
       </c>
       <c r="F26">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="H26">
         <v>76</v>

--- a/resultados/ConR/criterioB/resumen_parametros_ConR.xlsx
+++ b/resultados/ConR/criterioB/resumen_parametros_ConR.xlsx
@@ -406,10 +406,10 @@
         <v>216517</v>
       </c>
       <c r="D2">
-        <v>332</v>
+        <v>340</v>
       </c>
       <c r="F2">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="H2">
         <v>56</v>
@@ -425,13 +425,13 @@
         <v>2182.1</v>
       </c>
       <c r="D3">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="F3">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H3">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="4">
@@ -488,7 +488,7 @@
         <v>2</v>
       </c>
       <c r="H6">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="7">
@@ -539,10 +539,10 @@
         <v>178347</v>
       </c>
       <c r="D9">
-        <v>188</v>
+        <v>184</v>
       </c>
       <c r="F9">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="H9">
         <v>28</v>
@@ -634,10 +634,10 @@
         <v>354288</v>
       </c>
       <c r="D14">
-        <v>568</v>
+        <v>572</v>
       </c>
       <c r="F14">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="H14">
         <v>89</v>
@@ -716,7 +716,7 @@
         <v>5</v>
       </c>
       <c r="H18">
-        <v>4</v>
+        <v>9</v>
       </c>
     </row>
     <row r="19">
@@ -751,7 +751,7 @@
         <v>80</v>
       </c>
       <c r="F20">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H20">
         <v>17</v>
@@ -770,7 +770,7 @@
         <v>28</v>
       </c>
       <c r="F21">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H21">
         <v>5</v>
@@ -789,7 +789,7 @@
         <v>16</v>
       </c>
       <c r="F22">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H22">
         <v>4</v>
@@ -805,7 +805,7 @@
         <v>196810</v>
       </c>
       <c r="D23">
-        <v>156</v>
+        <v>160</v>
       </c>
       <c r="F23">
         <v>33</v>
@@ -827,7 +827,7 @@
         <v>152</v>
       </c>
       <c r="F24">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="H24">
         <v>29</v>
@@ -849,7 +849,7 @@
         <v>1</v>
       </c>
       <c r="H25">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="26">
@@ -862,7 +862,7 @@
         <v>992143</v>
       </c>
       <c r="D26">
-        <v>364</v>
+        <v>360</v>
       </c>
       <c r="F26">
         <v>83</v>

--- a/resultados/ConR/criterioB/resumen_parametros_ConR.xlsx
+++ b/resultados/ConR/criterioB/resumen_parametros_ConR.xlsx
@@ -406,10 +406,10 @@
         <v>216517</v>
       </c>
       <c r="D2">
-        <v>340</v>
+        <v>336</v>
       </c>
       <c r="F2">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="H2">
         <v>56</v>
@@ -561,7 +561,7 @@
         <v>444</v>
       </c>
       <c r="F10">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="H10">
         <v>75</v>
@@ -580,7 +580,7 @@
         <v>116</v>
       </c>
       <c r="F11">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H11">
         <v>19</v>
@@ -634,10 +634,10 @@
         <v>354288</v>
       </c>
       <c r="D14">
-        <v>572</v>
+        <v>568</v>
       </c>
       <c r="F14">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="H14">
         <v>89</v>
@@ -691,7 +691,7 @@
         <v>150772</v>
       </c>
       <c r="D17">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="F17">
         <v>20</v>
@@ -710,7 +710,7 @@
         <v>29789.9</v>
       </c>
       <c r="D18">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="F18">
         <v>5</v>
@@ -751,7 +751,7 @@
         <v>80</v>
       </c>
       <c r="F20">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="H20">
         <v>17</v>
@@ -805,10 +805,10 @@
         <v>196810</v>
       </c>
       <c r="D23">
-        <v>160</v>
+        <v>156</v>
       </c>
       <c r="F23">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="H23">
         <v>28</v>
@@ -865,7 +865,7 @@
         <v>360</v>
       </c>
       <c r="F26">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="H26">
         <v>76</v>
